--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\qr-attendance-system\excel_data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\qr-attendance-system\attendance-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC882FFA-3066-4E5E-ADAE-7D9C6241BD23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A17023-4670-474F-A6E7-29D87E09B831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{261448AB-2E93-4BD5-B3EC-E15FDBA68292}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
   <si>
     <t>Name</t>
   </si>
@@ -64,6 +64,12 @@
   </si>
   <si>
     <t>Aditi</t>
+  </si>
+  <si>
+    <t>B01</t>
+  </si>
+  <si>
+    <t>A01</t>
   </si>
 </sst>
 </file>
@@ -457,8 +463,8 @@
       <c r="B2" s="2">
         <v>12</v>
       </c>
-      <c r="C2" s="2">
-        <v>1234</v>
+      <c r="C2" s="2" t="s">
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>8</v>
@@ -475,8 +481,8 @@
       <c r="B3" s="2">
         <v>15</v>
       </c>
-      <c r="C3" s="2">
-        <v>1235</v>
+      <c r="C3" s="2" t="s">
+        <v>10</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>8</v>

--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\qr-attendance-system\attendance-backend\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86A17023-4670-474F-A6E7-29D87E09B831}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAB7FEEE-1E02-4E02-9FD6-506278A0CBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{261448AB-2E93-4BD5-B3EC-E15FDBA68292}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="14">
   <si>
     <t>Name</t>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <t>A01</t>
+  </si>
+  <si>
+    <t>Rohit</t>
+  </si>
+  <si>
+    <t>A02</t>
   </si>
 </sst>
 </file>
@@ -493,11 +499,21 @@
       <c r="F3" s="2"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2">
+        <v>23</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
